--- a/JO11-1/JO11-1_Volunteers.xlsx
+++ b/JO11-1/JO11-1_Volunteers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLTSWIERZE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/Misc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09B6198-A807-441B-A5C6-48065129ABAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{10C38519-2AD8-44E1-B2A9-944A26B4DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC10A1AA-F4D6-4AFA-B610-62D953B6EEC7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11130" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Volunteers_table" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Game</t>
   </si>
@@ -132,11 +132,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -147,6 +149,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -513,23 +516,23 @@
         <v>13</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K10" si="0">COUNTIF(E$2:E$963,$J2)*2</f>
+        <f t="shared" ref="K2:K10" si="0">COUNTIF(E$2:E$962,$J2)*2</f>
         <v>2</v>
       </c>
       <c r="L2" s="9">
-        <f t="shared" ref="L2:N2" si="1">COUNTIF(F$2:F$963,$J2)</f>
+        <f t="shared" ref="L2:L10" si="1">COUNTIF(F$2:F$962,$J2)</f>
         <v>0</v>
       </c>
       <c r="M2" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M2:M10" si="2">COUNTIF(G$2:G$962,$J2)</f>
         <v>0</v>
       </c>
       <c r="N2" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="N2:N10" si="3">COUNTIF(H$2:H$962,$J2)</f>
         <v>0</v>
       </c>
       <c r="O2" s="9">
-        <f t="shared" ref="O2:O10" si="2">SUM(K2:N2)</f>
+        <f t="shared" ref="O2:O10" si="4">SUM(K2:N2)</f>
         <v>2</v>
       </c>
     </row>
@@ -563,14 +566,14 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="9">
-        <f t="shared" ref="L3:N3" si="3">COUNTIF(F$2:F$963,$J3)</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="M3" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N3" s="9">
@@ -578,8 +581,8 @@
         <v>1</v>
       </c>
       <c r="O3" s="9">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -613,25 +616,25 @@
         <v>0</v>
       </c>
       <c r="L4" s="9">
-        <f t="shared" ref="L4:N4" si="4">COUNTIF(F$2:F$963,$J4)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="M4" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O4" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="N4" s="9">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O4" s="9">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5">
         <v>46256</v>
@@ -662,40 +665,46 @@
         <v>2</v>
       </c>
       <c r="L5" s="9">
-        <f t="shared" ref="L5:N5" si="5">COUNTIF(F$2:F$963,$J5)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N5" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O5" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>12</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>19</v>
@@ -705,46 +714,46 @@
         <v>0</v>
       </c>
       <c r="L6" s="9">
-        <f t="shared" ref="L6:N6" si="6">COUNTIF(F$2:F$963,$J6)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N6" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O6" s="9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>46270</v>
+        <v>46277</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>20</v>
@@ -754,97 +763,96 @@
         <v>0</v>
       </c>
       <c r="L7" s="9">
-        <f t="shared" ref="L7:N7" si="7">COUNTIF(F$2:F$963,$J7)</f>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="M7" s="9">
-        <f t="shared" si="7"/>
+      <c r="N7" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="4"/>
         <v>1</v>
-      </c>
-      <c r="N7" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O7" s="9">
-        <f t="shared" si="2"/>
-        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="7" t="str">
-        <f>J8</f>
-        <v>Johan</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="str">
-        <f>J7</f>
-        <v>Jesse</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>12</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="9">
-        <f t="shared" ref="L8:N8" si="8">COUNTIF(F$2:F$963,$J8)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="N8" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O8" s="9">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="11" t="str">
+        <f>J2</f>
+        <v>Adam</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>22</v>
@@ -854,28 +862,28 @@
         <v>4</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" ref="L9:N9" si="9">COUNTIF(F$2:F$963,$J9)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
       <c r="A10" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>16</v>
@@ -883,15 +891,15 @@
       <c r="D10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="11" t="str">
-        <f>J2</f>
-        <v>Adam</v>
-      </c>
-      <c r="F10" s="11" t="s">
+      <c r="E10" s="7" t="str">
+        <f>J5</f>
+        <v>Ilay</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>12</v>
@@ -904,49 +912,23 @@
         <v>0</v>
       </c>
       <c r="L10" s="9">
-        <f t="shared" ref="L10:N10" si="10">COUNTIF(F$2:F$963,$J10)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M10" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N10" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O10" s="9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="4">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46298</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="7" t="str">
-        <f>J5</f>
-        <v>Ilay</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="12" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="13" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="14" spans="1:15" ht="15.75" customHeight="1"/>
@@ -976,7 +958,10 @@
     <row r="38" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="40" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A41" s="12"/>
+      <c r="B41" s="12"/>
+    </row>
     <row r="42" spans="1:2" ht="15.75" customHeight="1">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
@@ -1469,10 +1454,7 @@
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
     </row>
-    <row r="165" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A165" s="12"/>
-      <c r="B165" s="12"/>
-    </row>
+    <row r="165" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="166" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="167" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="168" spans="1:2" ht="15.75" customHeight="1"/>

--- a/JO11-1/JO11-1_Volunteers.xlsx
+++ b/JO11-1/JO11-1_Volunteers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/Misc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/PRV/RKAVIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{10C38519-2AD8-44E1-B2A9-944A26B4DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC10A1AA-F4D6-4AFA-B610-62D953B6EEC7}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{10C38519-2AD8-44E1-B2A9-944A26B4DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55A2602F-B9B2-4473-A296-0FB4114FB48A}"/>
   <bookViews>
-    <workbookView xWindow="-11130" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Volunteers_table" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
   <si>
     <t>Game</t>
   </si>
@@ -517,7 +517,7 @@
       </c>
       <c r="K2" s="9">
         <f t="shared" ref="K2:K10" si="0">COUNTIF(E$2:E$962,$J2)*2</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" s="9">
         <f t="shared" ref="L2:L10" si="1">COUNTIF(F$2:F$962,$J2)</f>
@@ -533,7 +533,7 @@
       </c>
       <c r="O2" s="9">
         <f t="shared" ref="O2:O10" si="4">SUM(K2:N2)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
@@ -625,11 +625,11 @@
       </c>
       <c r="N4" s="9">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
@@ -662,7 +662,7 @@
       </c>
       <c r="K5" s="9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="9">
         <f t="shared" si="1"/>
@@ -670,7 +670,7 @@
       </c>
       <c r="M5" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="9">
         <f t="shared" si="3"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="O5" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
@@ -711,7 +711,7 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="9">
         <f t="shared" si="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="M6" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="9">
         <f t="shared" si="3"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="O6" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
@@ -768,7 +768,7 @@
       </c>
       <c r="M7" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="9">
         <f t="shared" si="3"/>
@@ -776,7 +776,7 @@
       </c>
       <c r="O7" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
@@ -801,15 +801,13 @@
       <c r="G8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="H8" s="7"/>
       <c r="J8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="K8" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="1"/>
@@ -825,7 +823,7 @@
       </c>
       <c r="O8" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
@@ -841,15 +839,14 @@
       <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="11" t="str">
-        <f>J2</f>
-        <v>Adam</v>
+      <c r="E9" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>20</v>
+      <c r="G9" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>12</v>
@@ -891,15 +888,14 @@
       <c r="D10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="7" t="str">
-        <f>J5</f>
-        <v>Ilay</v>
+      <c r="E10" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>12</v>

--- a/JO11-1/JO11-1_Volunteers.xlsx
+++ b/JO11-1/JO11-1_Volunteers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://warnermedia-my.sharepoint.com/personal/tomasz_swierzewski_wbd_com/Documents/PRV/RKAVIC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{10C38519-2AD8-44E1-B2A9-944A26B4DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55A2602F-B9B2-4473-A296-0FB4114FB48A}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{10C38519-2AD8-44E1-B2A9-944A26B4DAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C9C05C7-7CE5-40B6-8039-515B72BC7A60}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3465" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Volunteers_table" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="26">
   <si>
     <t>Game</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>Yahya</t>
+  </si>
+  <si>
+    <t>Kay</t>
+  </si>
+  <si>
+    <t>Noam</t>
   </si>
 </sst>
 </file>
@@ -516,23 +522,23 @@
         <v>13</v>
       </c>
       <c r="K2" s="9">
-        <f t="shared" ref="K2:K10" si="0">COUNTIF(E$2:E$962,$J2)*2</f>
+        <f t="shared" ref="K2:K12" si="0">COUNTIF(E$2:E$962,$J2)*2</f>
         <v>0</v>
       </c>
       <c r="L2" s="9">
-        <f t="shared" ref="L2:L10" si="1">COUNTIF(F$2:F$962,$J2)</f>
+        <f t="shared" ref="L2:L12" si="1">COUNTIF(F$2:F$962,$J2)</f>
         <v>0</v>
       </c>
       <c r="M2" s="9">
-        <f t="shared" ref="M2:M10" si="2">COUNTIF(G$2:G$962,$J2)</f>
+        <f t="shared" ref="M2:M12" si="2">COUNTIF(G$2:G$962,$J2)</f>
         <v>0</v>
       </c>
       <c r="N2" s="9">
-        <f t="shared" ref="N2:N10" si="3">COUNTIF(H$2:H$962,$J2)</f>
+        <f t="shared" ref="N2:N12" si="3">COUNTIF(H$2:H$962,$J2)</f>
         <v>0</v>
       </c>
       <c r="O2" s="9">
-        <f t="shared" ref="O2:O10" si="4">SUM(K2:N2)</f>
+        <f t="shared" ref="O2:O12" si="4">SUM(K2:N2)</f>
         <v>0</v>
       </c>
     </row>
@@ -566,11 +572,11 @@
       </c>
       <c r="K3" s="9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="9">
         <f t="shared" si="2"/>
@@ -582,7 +588,7 @@
       </c>
       <c r="O3" s="9">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -617,7 +623,7 @@
       </c>
       <c r="L4" s="9">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="9">
         <f t="shared" si="2"/>
@@ -629,7 +635,7 @@
       </c>
       <c r="O4" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
@@ -670,7 +676,7 @@
       </c>
       <c r="M5" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="9">
         <f t="shared" si="3"/>
@@ -678,7 +684,7 @@
       </c>
       <c r="O5" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
@@ -711,11 +717,11 @@
       </c>
       <c r="K6" s="9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" s="9">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="9">
         <f t="shared" si="2"/>
@@ -727,7 +733,7 @@
       </c>
       <c r="O6" s="9">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
@@ -768,7 +774,7 @@
       </c>
       <c r="M7" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="9">
         <f t="shared" si="3"/>
@@ -776,7 +782,7 @@
       </c>
       <c r="O7" s="9">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
@@ -807,7 +813,7 @@
       </c>
       <c r="K8" s="9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="1"/>
@@ -823,7 +829,7 @@
       </c>
       <c r="O8" s="9">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
@@ -856,7 +862,7 @@
       </c>
       <c r="K9" s="9">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="1"/>
@@ -872,7 +878,7 @@
       </c>
       <c r="O9" s="9">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
@@ -889,7 +895,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>15</v>
@@ -924,28 +930,200 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46319</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46326</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46333</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46340</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46347</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46354</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46361</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1"/>
     <row r="33" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="34" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="35" spans="1:2" ht="15.75" customHeight="1"/>
